--- a/testData/OpenCart_LoginData.xlsx
+++ b/testData/OpenCart_LoginData.xlsx
@@ -3,7 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{2525AB98-C8F7-4962-B517-BB212A0BBD3F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edify\eclipse-workspace\OpenCart\testData\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A783DD4-3D70-4A8E-B3A0-54818E720578}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{F8F2FF3E-43AB-4C4F-A610-3C06807957D0}"/>
   </bookViews>
@@ -11,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -425,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E8B247F-01C1-4121-9B25-E6B02A7ED2B2}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.6328125" bestFit="1" customWidth="1"/>
@@ -433,7 +437,7 @@
     <col min="3" max="3" width="6.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -444,7 +448,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -455,61 +459,61 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C6" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="G4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="G5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="G6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I6" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{D9F73030-30B6-401C-A0D6-38F5B7C24050}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{6A1C4444-E71E-4233-AE91-831C9E4D5407}"/>
-    <hyperlink ref="B3" r:id="rId3" xr:uid="{04C3FC6A-C136-4FE2-A2CC-22B94954DE8F}"/>
-    <hyperlink ref="G4" r:id="rId4" xr:uid="{FBB40A63-C8AF-4723-885B-C22EAFD37F04}"/>
-    <hyperlink ref="G5" r:id="rId5" xr:uid="{26EA3814-E3C1-4D85-B764-A3AE9C0E9983}"/>
-    <hyperlink ref="G6" r:id="rId6" xr:uid="{53BAB2A1-A7EA-4E59-A6FA-31967DCC9D10}"/>
-    <hyperlink ref="H4" r:id="rId7" xr:uid="{F7B50C67-4F9A-410D-98F1-131EABF35041}"/>
-    <hyperlink ref="H5" r:id="rId8" xr:uid="{FBAB5E3E-87C4-4E99-85BC-35EEE07A8255}"/>
-    <hyperlink ref="H6" r:id="rId9" xr:uid="{17F6C93F-898D-40A6-AC6A-00646B5332D7}"/>
+    <hyperlink ref="A6" r:id="rId2" xr:uid="{6A1C4444-E71E-4233-AE91-831C9E4D5407}"/>
+    <hyperlink ref="B6" r:id="rId3" xr:uid="{04C3FC6A-C136-4FE2-A2CC-22B94954DE8F}"/>
+    <hyperlink ref="A3" r:id="rId4" xr:uid="{FBB40A63-C8AF-4723-885B-C22EAFD37F04}"/>
+    <hyperlink ref="A4" r:id="rId5" xr:uid="{26EA3814-E3C1-4D85-B764-A3AE9C0E9983}"/>
+    <hyperlink ref="A5" r:id="rId6" xr:uid="{53BAB2A1-A7EA-4E59-A6FA-31967DCC9D10}"/>
+    <hyperlink ref="B3" r:id="rId7" xr:uid="{F7B50C67-4F9A-410D-98F1-131EABF35041}"/>
+    <hyperlink ref="B4" r:id="rId8" xr:uid="{FBAB5E3E-87C4-4E99-85BC-35EEE07A8255}"/>
+    <hyperlink ref="B5" r:id="rId9" xr:uid="{17F6C93F-898D-40A6-AC6A-00646B5332D7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
